--- a/光伏配储项目/电价数据/2026/阳江站.xlsx
+++ b/光伏配储项目/电价数据/2026/阳江站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50979</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.70248</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56431</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.50898</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44567</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45467</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089100000000001</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42073</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41305</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44423</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26123</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21052</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07493000000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06201</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05062</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03834000000000001</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04208</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.00256</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.03214</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08576</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.02032</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.005820000000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00145</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14473</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21273</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.2349</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18495</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11056</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.01947</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01003</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.11169</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11696</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.17141</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22008</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.16705</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.14153</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.11788</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.18727</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.24852</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.03371</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.21444</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.45158</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.42919</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52534</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.47706</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7360800000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61037</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.50826</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.50301</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.03615</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5742</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5361699999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.24209</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.49586</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.49867</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.59453</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.55372</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43126</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47963</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42175</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62166</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.42023</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.74349</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.99862</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7990499999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53686</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50664</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50607</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50229</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47433</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37357</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42295</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.51667</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.62924</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72061</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44664</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.08787</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04614</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26175</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.26783</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.27432</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.2448</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.60149</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.17636</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27701</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.24933</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.5774900000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.01794</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27211</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.23193</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.16986</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23234</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.2377</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23187</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.2505</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.2426</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.44325</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.25796</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68712</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79367</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7870499999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.24163</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.80337</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.7719199999999999</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43546</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5896399999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4387</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43292</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33333</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51525</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.46602</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47401</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44816</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44252</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27739</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.13672</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.27604</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.2511</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.40789</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.24434</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.26857</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.06922</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21328</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.14633</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20464</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.19227</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24759</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27974</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.2721</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.22849</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.006990000000000001</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.47294</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.02623</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.49887</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.28694</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34339</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47021</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28192</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26308</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.21485</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.13196</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.12689</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.09345000000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.22635</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.12668</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28665</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.4529</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21047</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04615</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06506000000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.26179</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.21039</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.0524</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.00152</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.004019999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.04167</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.07759999999999999</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.11131</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.25247</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.19465</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.22319</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.18193</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.23161</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16176</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.23595</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.25203</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.27204</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48468</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.27806</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29099</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.28679</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04014</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04533</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.03993</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03978</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04297</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04457</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04189</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.0465</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04608</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04445</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04459</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04453</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04348</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04589</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04914</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04499</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04568</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04714</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04704999999999999</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04498</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04695000000000001</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22032</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04732</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05349</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00258</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14647</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03688</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09843</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41761</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35139</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6635800000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10242</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04246</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04629</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04258</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03195</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04137</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10654</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03766</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04707</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04211</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04221</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.0421</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04439</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0443</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04429</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04206</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0415</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04131</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03983</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04493</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04402</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04431</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04186</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04289</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04049000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04296</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04376</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04685</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04674</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20147</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14406</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29245</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27045</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33699</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32079</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27269</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27267</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17362</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15987</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17244</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14893</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16065</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15996</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23838</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21538</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22792</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27107</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28231</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.26938</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28235</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.27228</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.43046</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.40888</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.40567</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15736</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.28304</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38203</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79111</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6218899999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49775</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78083</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.91995</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49424</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92314</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8924</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31126</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9153600000000001</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6361599999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.21441</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8821599999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.56565</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.35895</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.05216</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5590599999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.81508</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7971900000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.79675</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87975</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88652</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.51578</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42897</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.47579</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.23607</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87967</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55153</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.65067</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5455099999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50598</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45934</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44223</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45305</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42149</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58869</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59662</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60156</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.65599</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5585</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44639</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86195</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6547200000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8289800000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.81196</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.84839</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45289</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35338</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.98685</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.48733</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.45062</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.54422</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.61225</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.40284</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.41797</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.45858</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.41264</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16456</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28109</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26083</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20053</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.25617</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27498</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.26951</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27546</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43196</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44777</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5978300000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88966</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.3505</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1405</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7072999999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8000499999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65232</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58763</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45121</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43774</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.55186</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.06181</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5795800000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.6604500000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.21873</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.53792</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26544</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26564</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29409</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.43725</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40558</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.58625</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46447</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7156699999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46581</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43868</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42462</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32569</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.26357</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27194</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23583</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14494</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14726</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15411</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14438</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14078</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14415</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25739</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14469</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26672</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26711</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14213</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.03421</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11415</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11326</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14537</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14148</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14666</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28736</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45082</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44104</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44539</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44485</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35008</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5497799999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46975</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41682</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39396</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27473</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.24381</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23923</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.1836</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.23992</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.22025</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.24541</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.27414</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.26726</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28695</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.28537</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27157</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.22031</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28017</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.27812</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.26193</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41972</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24376</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36055</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28177</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.41001</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.27594</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26715</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03814</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25137</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25002</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07113</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.17979</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24456</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28538</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.26841</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25019</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.28627</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.26946</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46923</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40462</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7327100000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.40924</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46027</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30106</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40458</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28615</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.6013999999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43127</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6565299999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8486</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47749</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.42049</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46094</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34505</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26077</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.1341</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28248</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19475</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24497</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.02259</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.11339</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.02272</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23071</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24045</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14412</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.20956</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.21695</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.28572</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41659</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.65964</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6228899999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.61803</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.47001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6411</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47954</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.7894</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45125</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46272</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48219</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43171</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42078</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36023</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49351</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.47175</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46762</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42079</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40655</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41345</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41946</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39748</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41359</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4111</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41983</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45217</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45122</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56449</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5031600000000001</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45232</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41418</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.28694</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.24333</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.26667</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.12646</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.00409</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.01133</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.66437</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.26849</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.12094</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.08419</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.04115</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.25772</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.00671</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41797</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48766</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42979</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.51063</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.51236</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.58427</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.70517</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.7028799999999999</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.68079</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.76877</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.55015</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5266799999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83412</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7675700000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6142000000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6651699999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.44825</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48536</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48149</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47526</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.54152</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42585</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46055</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4387799999999999</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42797</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45036</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41924</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40164</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46005</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27281</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15519</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27233</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04497</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45421</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40617</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46489</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.04067</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18381</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40839</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40055</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36405</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44382</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24637</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23267</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23416</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.23431</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24769</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.00292</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13227</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.01066</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.15994</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25614</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.00426</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14517</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15348</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.03011</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.04004</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21694</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22863</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.15212</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21447</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26684</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28361</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.26236</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35227</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22668</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21675</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15096</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.17981</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.07248</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01608</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.06249</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03346</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04158</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.03316</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.0442</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.04207</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.16942</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21463</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27696</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24566</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24618</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25047</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26331</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28661</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27192</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26841</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25688</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27666</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28022</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26518</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26754</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25485</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26646</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25086</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23427</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.17813</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05531</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.40735</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.01337</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06419</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.24846</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22465</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22455</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.14372</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26944</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26096</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24321</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22156</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20581</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.18902</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21299</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22572</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.16926</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.1893</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22284</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.21932</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24401</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.2318</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21467</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26101</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.2252</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.2686</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27062</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2463</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24925</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18363</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06393</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.49032</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.49857</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.54698</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.07492</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.22749</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02123</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.20203</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09314</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.04234</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.05537</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20801</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.00123</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02637</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03870000000000001</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.04029</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.08170999999999999</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02579</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.01644</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02819</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.04749</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23625</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25386</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.21224</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32531</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.11275</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27693</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.41101</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.26174</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25523</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.14275</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24556</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.11347</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25775</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26974</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.07362</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3312</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.26306</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27702</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.50769</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50604</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.26015</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.28584</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.26415</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.25972</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.16509</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26041</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.27918</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.25825</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25876</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.23713</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27568</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.26615</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.27602</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42166</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40449</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47175</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.48501</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46529</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.47769</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.04457</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.43919</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47429</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.43499</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.42085</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42582</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.74199</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45283</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40701</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36899</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46821</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.20441</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.15822</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23725</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29245</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26548</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.17521</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26945</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43645</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41008</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39431</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46422</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56045</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5566599999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45893</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.54762</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46343</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49589</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5353600000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5269199999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7300399999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.77247</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54862</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55077</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44362</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37566</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28593</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.28027</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27379</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.25959</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.26002</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27565</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20966</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23405</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.15673</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.02131</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.14081</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01516</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.13597</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01143</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.04065999999999999</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02386</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.0407</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02178</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03351</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02568</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.02272</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.03045</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.12175</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.07496</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.13224</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.15896</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.19284</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.24823</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.16188</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.22444</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.27015</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37847</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.81041</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.28198</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.25948</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.24973</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.22105</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.22026</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.22465</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24298</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.08746</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01126</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.00992</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.008960000000000001</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03401</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.11882</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.02946</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.0057</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01551</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04417</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01205</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.009679999999999999</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01547</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.1555</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.18007</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.03345</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.17296</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13567</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.15658</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.18352</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.1766</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.24811</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.19907</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.26455</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.22695</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.26037</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44849</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5182100000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41467</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39279</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38071</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42459</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38437</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3862</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.52198</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25428</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.21813</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.19894</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.12711</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.17607</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.20117</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.19548</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.09942000000000001</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.12561</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.05775</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.08083</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04088</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04184</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04109</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04436</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04714</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06874</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.0602</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.08348999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.14043</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.16536</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.10202</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.20823</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.18232</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.23672</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.1188</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.10267</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2091</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.15636</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.18746</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.20241</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.17319</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21134</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23567</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23689</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.25363</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39253</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40755</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49486</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40736</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42978</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41056</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40827</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38413</v>
       </c>
     </row>
   </sheetData>
